--- a/sampleprojects/TaxReturn/excel/states/AR.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/AR.xlsx
@@ -81,19 +81,19 @@
     <t>Calculate Arkansas tax - Married filing jointly (5-tier progressive: 0%/2%/3%/3.4%/3.9%). NOTE: result.ar_taxable_income / result.ar_state_tax not declared in AR_edd — EDD authorship needed.</t>
   </si>
   <si>
-    <t>set result.ar_taxable_income = the maximum of (result.agi - ar_standard_deduction_joint) and 0.0; set result.ar_state_tax = (the minimum of result.ar_taxable_income and ar_bracket_1_limit) * ar_bracket_1_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_2_limit) - ar_bracket_1_limit) and 0.0) * ar_bracket_2_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_3_limit) - ar_bracket_2_limit) and 0.0) * ar_bracket_3_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_4_limit) - ar_bracket_3_limit) and 0.0) * ar_bracket_4_rate + (the maximum of (result.ar_taxable_income - ar_bracket_4_limit) and 0.0) * ar_bracket_5_rate; add "  AR tax (MFJ, 5 brackets): $" + result.ar_state_tax to job.audit_trail</t>
+    <t>set result.ar_taxable_income = the maximum of (result.state_calc_agi - ar_standard_deduction_joint) and 0.0; set result.ar_state_tax = (the minimum of result.ar_taxable_income and ar_bracket_1_limit) * ar_bracket_1_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_2_limit) - ar_bracket_1_limit) and 0.0) * ar_bracket_2_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_3_limit) - ar_bracket_2_limit) and 0.0) * ar_bracket_3_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_4_limit) - ar_bracket_3_limit) and 0.0) * ar_bracket_4_rate + (the maximum of (result.ar_taxable_income - ar_bracket_4_limit) and 0.0) * ar_bracket_5_rate; add "  AR tax (MFJ, 5 brackets): $" + result.ar_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>Calculate Arkansas tax - Head of household (5-tier progressive: 0%/2%/3%/3.4%/3.9%).</t>
   </si>
   <si>
-    <t>set result.ar_taxable_income = the maximum of (result.agi - ar_standard_deduction_hoh) and 0.0; set result.ar_state_tax = (the minimum of result.ar_taxable_income and ar_bracket_1_limit) * ar_bracket_1_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_2_limit) - ar_bracket_1_limit) and 0.0) * ar_bracket_2_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_3_limit) - ar_bracket_2_limit) and 0.0) * ar_bracket_3_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_4_limit) - ar_bracket_3_limit) and 0.0) * ar_bracket_4_rate + (the maximum of (result.ar_taxable_income - ar_bracket_4_limit) and 0.0) * ar_bracket_5_rate; add "  AR tax (HOH, 5 brackets): $" + result.ar_state_tax to job.audit_trail</t>
+    <t>set result.ar_taxable_income = the maximum of (result.state_calc_agi - ar_standard_deduction_hoh) and 0.0; set result.ar_state_tax = (the minimum of result.ar_taxable_income and ar_bracket_1_limit) * ar_bracket_1_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_2_limit) - ar_bracket_1_limit) and 0.0) * ar_bracket_2_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_3_limit) - ar_bracket_2_limit) and 0.0) * ar_bracket_3_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_4_limit) - ar_bracket_3_limit) and 0.0) * ar_bracket_4_rate + (the maximum of (result.ar_taxable_income - ar_bracket_4_limit) and 0.0) * ar_bracket_5_rate; add "  AR tax (HOH, 5 brackets): $" + result.ar_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>Calculate Arkansas tax - Married filing separately (5-tier progressive: 0%/2%/3%/3.4%/3.9%).</t>
   </si>
   <si>
-    <t>set result.ar_taxable_income = the maximum of (result.agi - ar_standard_deduction_mfs) and 0.0; set result.ar_state_tax = (the minimum of result.ar_taxable_income and ar_bracket_1_limit) * ar_bracket_1_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_2_limit) - ar_bracket_1_limit) and 0.0) * ar_bracket_2_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_3_limit) - ar_bracket_2_limit) and 0.0) * ar_bracket_3_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_4_limit) - ar_bracket_3_limit) and 0.0) * ar_bracket_4_rate + (the maximum of (result.ar_taxable_income - ar_bracket_4_limit) and 0.0) * ar_bracket_5_rate; add "  AR tax (MFS, 5 brackets): $" + result.ar_state_tax to job.audit_trail</t>
+    <t>set result.ar_taxable_income = the maximum of (result.state_calc_agi - ar_standard_deduction_mfs) and 0.0; set result.ar_state_tax = (the minimum of result.ar_taxable_income and ar_bracket_1_limit) * ar_bracket_1_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_2_limit) - ar_bracket_1_limit) and 0.0) * ar_bracket_2_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_3_limit) - ar_bracket_2_limit) and 0.0) * ar_bracket_3_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_4_limit) - ar_bracket_3_limit) and 0.0) * ar_bracket_4_rate + (the maximum of (result.ar_taxable_income - ar_bracket_4_limit) and 0.0) * ar_bracket_5_rate; add "  AR tax (MFS, 5 brackets): $" + result.ar_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>DT: AR Military Retirement Exclusion</t>

--- a/sampleprojects/TaxReturn/excel/states/AR.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/AR.xlsx
@@ -9,14 +9,15 @@
   <sheets>
     <sheet name="AR Tax" sheetId="2" r:id="rId4"/>
     <sheet name="AR Military Retirement Exclusio" sheetId="3" r:id="rId6"/>
-    <sheet name="EDD" sheetId="4" r:id="rId7"/>
+    <sheet name="AR Tax Table" sheetId="4" r:id="rId7"/>
+    <sheet name="EDD" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
   <si>
     <t>DT: AR Tax</t>
   </si>
@@ -42,34 +43,37 @@
     <t>DSL: INITIAL ACTIONS</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>set result.ar_std_deduction = ar_standard_deduction_single; set result.ar_extra_credits = 0.0</t>
+  </si>
+  <si>
     <t>CONDITIONS: COMMENTS</t>
   </si>
   <si>
     <t>DSL: CONDITIONS</t>
   </si>
   <si>
-    <t>Married filing jointly</t>
-  </si>
-  <si>
-    <t>filing_status == "MFJ"</t>
+    <t>Married Filing Joint</t>
+  </si>
+  <si>
+    <t>job.filing_status is equal to "MFJ"</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>Head of household</t>
-  </si>
-  <si>
-    <t>filing_status == "HOH"</t>
-  </si>
-  <si>
-    <t>Married filing separately</t>
-  </si>
-  <si>
-    <t>filing_status == "MFS"</t>
+    <t>Head of Household or Surviving Spouse: one extra personal credit</t>
+  </si>
+  <si>
+    <t>job.filing_status is equal to "HOH" or job.filing_status is equal to "QSS"</t>
+  </si>
+  <si>
+    <t>*</t>
   </si>
   <si>
     <t>ACTIONS: COMMENTS</t>
@@ -78,22 +82,49 @@
     <t>DSL: ACTIONS</t>
   </si>
   <si>
-    <t>Calculate Arkansas tax - Married filing jointly (5-tier progressive: 0%/2%/3%/3.4%/3.9%). NOTE: result.ar_taxable_income / result.ar_state_tax not declared in AR_edd — EDD authorship needed.</t>
-  </si>
-  <si>
-    <t>set result.ar_taxable_income = the maximum of (result.state_calc_agi - ar_standard_deduction_joint) and 0.0; set result.ar_state_tax = (the minimum of result.ar_taxable_income and ar_bracket_1_limit) * ar_bracket_1_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_2_limit) - ar_bracket_1_limit) and 0.0) * ar_bracket_2_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_3_limit) - ar_bracket_2_limit) and 0.0) * ar_bracket_3_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_4_limit) - ar_bracket_3_limit) and 0.0) * ar_bracket_4_rate + (the maximum of (result.ar_taxable_income - ar_bracket_4_limit) and 0.0) * ar_bracket_5_rate; add "  AR tax (MFJ, 5 brackets): $" + result.ar_state_tax to job.audit_trail</t>
-  </si>
-  <si>
-    <t>Calculate Arkansas tax - Head of household (5-tier progressive: 0%/2%/3%/3.4%/3.9%).</t>
-  </si>
-  <si>
-    <t>set result.ar_taxable_income = the maximum of (result.state_calc_agi - ar_standard_deduction_hoh) and 0.0; set result.ar_state_tax = (the minimum of result.ar_taxable_income and ar_bracket_1_limit) * ar_bracket_1_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_2_limit) - ar_bracket_1_limit) and 0.0) * ar_bracket_2_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_3_limit) - ar_bracket_2_limit) and 0.0) * ar_bracket_3_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_4_limit) - ar_bracket_3_limit) and 0.0) * ar_bracket_4_rate + (the maximum of (result.ar_taxable_income - ar_bracket_4_limit) and 0.0) * ar_bracket_5_rate; add "  AR tax (HOH, 5 brackets): $" + result.ar_state_tax to job.audit_trail</t>
-  </si>
-  <si>
-    <t>Calculate Arkansas tax - Married filing separately (5-tier progressive: 0%/2%/3%/3.4%/3.9%).</t>
-  </si>
-  <si>
-    <t>set result.ar_taxable_income = the maximum of (result.state_calc_agi - ar_standard_deduction_mfs) and 0.0; set result.ar_state_tax = (the minimum of result.ar_taxable_income and ar_bracket_1_limit) * ar_bracket_1_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_2_limit) - ar_bracket_1_limit) and 0.0) * ar_bracket_2_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_3_limit) - ar_bracket_2_limit) and 0.0) * ar_bracket_3_rate + (the maximum of ((the minimum of result.ar_taxable_income and ar_bracket_4_limit) - ar_bracket_3_limit) and 0.0) * ar_bracket_4_rate + (the maximum of (result.ar_taxable_income - ar_bracket_4_limit) and 0.0) * ar_bracket_5_rate; add "  AR tax (MFS, 5 brackets): $" + result.ar_state_tax to job.audit_trail</t>
+    <t>$4,940 standard deduction, MFJ</t>
+  </si>
+  <si>
+    <t>set result.ar_std_deduction = ar_standard_deduction_joint</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>AR1000F line 7A: HOH or Surviving Spouse box</t>
+  </si>
+  <si>
+    <t>set result.ar_extra_credits = 1.0</t>
+  </si>
+  <si>
+    <t>Line 28 net taxable income; line 29 tax from the Regular Tax Table</t>
+  </si>
+  <si>
+    <t>set result.ar_taxable_income = the maximum of (result.state_calc_agi - result.ar_std_deduction) and 0.0; perform AR_Tax_Table</t>
+  </si>
+  <si>
+    <t>Lines 7A-7C / 34: $29 each</t>
+  </si>
+  <si>
+    <t>set result.ar_personal_credits = (length of job.taxpayers + length of job.dependents + result.senior_std_count + result.ar_extra_credits) * ar_personal_tax_credit</t>
+  </si>
+  <si>
+    <t>Tax less personal tax credits</t>
+  </si>
+  <si>
+    <t>set result.ar_state_tax = the maximum of (result.ar_table_tax - result.ar_personal_credits) and 0.0</t>
+  </si>
+  <si>
+    <t>Harvested onto the roster by Compute_Roster_State_Tax</t>
+  </si>
+  <si>
+    <t>set result.computed_state_taxable_income = result.ar_taxable_income; set result.computed_state_tax = result.ar_state_tax</t>
+  </si>
+  <si>
+    <t>Audit</t>
+  </si>
+  <si>
+    <t>add "  Arkansas (AR1000F 2025): net taxable income $" + result.ar_taxable_income + ", table tax $" + result.ar_table_tax + ", personal credits $" + result.ar_personal_credits + ", tax $" + result.ar_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>DT: AR Military Retirement Exclusion</t>
@@ -105,6 +136,108 @@
     <t>TABLE_NUMBER: 40401</t>
   </si>
   <si>
+    <t>DT: AR Tax Table</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMENTS: </t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 40410</t>
+  </si>
+  <si>
+    <t>if result.ar_taxable_income &gt;= ar_table_band_shift then { set result.ar_band_midpoint = (the floor of ((result.ar_taxable_income - 1.0) / 100.0)) * 100.0 + 51.0; } else { set result.ar_band_midpoint = (the floor of (result.ar_taxable_income / 100.0)) * 100.0 + 50.0; } endif</t>
+  </si>
+  <si>
+    <t>Over $100,000: formula</t>
+  </si>
+  <si>
+    <t>result.ar_taxable_income &gt; ar_high_threshold</t>
+  </si>
+  <si>
+    <t>0% bracket</t>
+  </si>
+  <si>
+    <t>result.ar_band_midpoint &lt;= ar_bracket_1_limit</t>
+  </si>
+  <si>
+    <t>2% bracket</t>
+  </si>
+  <si>
+    <t>result.ar_band_midpoint &lt;= ar_bracket_2_limit</t>
+  </si>
+  <si>
+    <t>3% bracket</t>
+  </si>
+  <si>
+    <t>result.ar_band_midpoint &lt;= ar_bracket_3_limit</t>
+  </si>
+  <si>
+    <t>3.4% bracket</t>
+  </si>
+  <si>
+    <t>result.ar_band_midpoint &lt;= ar_bracket_4_limit</t>
+  </si>
+  <si>
+    <t>3.9% bracket</t>
+  </si>
+  <si>
+    <t>result.ar_band_midpoint &lt;= ar_bracket_5_limit</t>
+  </si>
+  <si>
+    <t>3.9%, adjustment phasing out $94,701-$97,800</t>
+  </si>
+  <si>
+    <t>result.ar_band_midpoint &lt;= ar_phase_limit</t>
+  </si>
+  <si>
+    <t>$3,809 + 3.9% of the excess over $100,000</t>
+  </si>
+  <si>
+    <t>set result.ar_table_tax = the floor of (ar_high_base + (result.ar_taxable_income - ar_high_threshold) * ar_bracket_5_rate + 0.5)</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>set result.ar_table_tax = 0.0</t>
+  </si>
+  <si>
+    <t>2% less $111.98</t>
+  </si>
+  <si>
+    <t>set result.ar_table_tax = the floor of (result.ar_band_midpoint * ar_bracket_2_rate - ar_bracket_2_adjust + 0.5)</t>
+  </si>
+  <si>
+    <t>3% less $223.97</t>
+  </si>
+  <si>
+    <t>set result.ar_table_tax = the floor of (result.ar_band_midpoint * ar_bracket_3_rate - ar_bracket_3_adjust + 0.5)</t>
+  </si>
+  <si>
+    <t>3.4% less $287.97</t>
+  </si>
+  <si>
+    <t>set result.ar_table_tax = the floor of (result.ar_band_midpoint * ar_bracket_4_rate - ar_bracket_4_adjust + 0.5)</t>
+  </si>
+  <si>
+    <t>3.9% less $419.96</t>
+  </si>
+  <si>
+    <t>set result.ar_table_tax = the floor of (result.ar_band_midpoint * ar_bracket_5_rate - ar_bracket_5_adjust + 0.5)</t>
+  </si>
+  <si>
+    <t>3.9% less $399.30, $10.00 less per $100 band from $94,701</t>
+  </si>
+  <si>
+    <t>set result.ar_table_tax = the floor of (result.ar_band_midpoint * ar_bracket_5_rate - (ar_phase_adjust_first - (the floor of ((result.ar_taxable_income - ar_bracket_5_limit - 1.0) / 100.0)) * ar_phase_adjust_step) + 0.5)</t>
+  </si>
+  <si>
+    <t>3.9% less $89.30, $97,801-$100,000</t>
+  </si>
+  <si>
+    <t>set result.ar_table_tax = the floor of (result.ar_band_midpoint * ar_bracket_5_rate - ar_top_adjust + 0.5)</t>
+  </si>
+  <si>
     <t>EDD: EDD</t>
   </si>
   <si>
@@ -150,22 +283,34 @@
     <t>result</t>
   </si>
   <si>
-    <t>(13 attributes)</t>
+    <t>(33 attributes)</t>
+  </si>
+  <si>
+    <t>ar_band_midpoint</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>rw</t>
+  </si>
+  <si>
+    <t>AR tax computation (AR_Tax)</t>
   </si>
   <si>
     <t>ar_bracket_1_limit</t>
   </si>
   <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>5499.0</t>
+    <t>5599</t>
   </si>
   <si>
     <t>r</t>
   </si>
   <si>
-    <t>AR tax bracket 1 upper limit - 0% rate (2025)</t>
+    <t>AR DFA 2025 Indexed Tax Brackets: 0% on net taxable income through $5,599</t>
   </si>
   <si>
     <t>ar_bracket_1_rate</t>
@@ -177,13 +322,22 @@
     <t>AR tax rate for bracket 1 - 0% (2025)</t>
   </si>
   <si>
+    <t>ar_bracket_2_adjust</t>
+  </si>
+  <si>
+    <t>111.98</t>
+  </si>
+  <si>
+    <t>AR DFA 2025 Indexed Tax Brackets: 2% bracket, minus adjustment</t>
+  </si>
+  <si>
     <t>ar_bracket_2_limit</t>
   </si>
   <si>
-    <t>10999.0</t>
-  </si>
-  <si>
-    <t>AR tax bracket 2 upper limit (2025)</t>
+    <t>11199</t>
+  </si>
+  <si>
+    <t>AR DFA 2025 Indexed Tax Brackets: 2% bracket top</t>
   </si>
   <si>
     <t>ar_bracket_2_rate</t>
@@ -195,13 +349,22 @@
     <t>AR tax rate for bracket 2 - 2% (2025)</t>
   </si>
   <si>
+    <t>ar_bracket_3_adjust</t>
+  </si>
+  <si>
+    <t>223.97</t>
+  </si>
+  <si>
+    <t>AR DFA 2025 Indexed Tax Brackets: 3% bracket, minus adjustment</t>
+  </si>
+  <si>
     <t>ar_bracket_3_limit</t>
   </si>
   <si>
-    <t>16999.0</t>
-  </si>
-  <si>
-    <t>AR tax bracket 3 upper limit (2025)</t>
+    <t>15999</t>
+  </si>
+  <si>
+    <t>AR DFA 2025 Indexed Tax Brackets: 3% bracket top</t>
   </si>
   <si>
     <t>ar_bracket_3_rate</t>
@@ -213,13 +376,22 @@
     <t>AR tax rate for bracket 3 - 3% (2025)</t>
   </si>
   <si>
+    <t>ar_bracket_4_adjust</t>
+  </si>
+  <si>
+    <t>287.97</t>
+  </si>
+  <si>
+    <t>AR DFA 2025 Indexed Tax Brackets: 3.4% bracket, minus adjustment</t>
+  </si>
+  <si>
     <t>ar_bracket_4_limit</t>
   </si>
   <si>
-    <t>25699.0</t>
-  </si>
-  <si>
-    <t>AR tax bracket 4 upper limit (2025)</t>
+    <t>26399</t>
+  </si>
+  <si>
+    <t>AR DFA 2025 Indexed Tax Brackets: 3.4% bracket top</t>
   </si>
   <si>
     <t>ar_bracket_4_rate</t>
@@ -231,6 +403,24 @@
     <t>AR tax rate for bracket 4 - 3.4% (2025)</t>
   </si>
   <si>
+    <t>ar_bracket_5_adjust</t>
+  </si>
+  <si>
+    <t>419.96</t>
+  </si>
+  <si>
+    <t>AR DFA 2025 Indexed Tax Brackets: 3.9% bracket, minus adjustment</t>
+  </si>
+  <si>
+    <t>ar_bracket_5_limit</t>
+  </si>
+  <si>
+    <t>94700</t>
+  </si>
+  <si>
+    <t>AR DFA 2025 Indexed Tax Brackets: 3.9% bracket top before the $94,701-$97,800 adjustment phase-in</t>
+  </si>
+  <si>
     <t>ar_bracket_5_rate</t>
   </si>
   <si>
@@ -240,34 +430,124 @@
     <t>AR tax rate for bracket 5 - 3.9% on income over $25,700 (2025)</t>
   </si>
   <si>
+    <t>ar_extra_credits</t>
+  </si>
+  <si>
+    <t>ar_high_base</t>
+  </si>
+  <si>
+    <t>3809</t>
+  </si>
+  <si>
+    <t>AR 2025 Tax Tables: $3,809 + 3.9% of the excess over $100,000</t>
+  </si>
+  <si>
+    <t>ar_high_threshold</t>
+  </si>
+  <si>
+    <t>100000</t>
+  </si>
+  <si>
+    <t>AR 2025 Tax Tables: over $100,000 the tax is a formula</t>
+  </si>
+  <si>
+    <t>ar_personal_credits</t>
+  </si>
+  <si>
+    <t>ar_personal_tax_credit</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>AR1000F line 7: $29 per personal tax credit</t>
+  </si>
+  <si>
+    <t>ar_phase_adjust_first</t>
+  </si>
+  <si>
+    <t>399.30</t>
+  </si>
+  <si>
+    <t>AR DFA 2025 Indexed Tax Brackets: minus adjustment for $94,701-$94,800</t>
+  </si>
+  <si>
+    <t>ar_phase_adjust_step</t>
+  </si>
+  <si>
+    <t>10.00</t>
+  </si>
+  <si>
+    <t>AR DFA 2025 Indexed Tax Brackets: the adjustment falls $10.00 per $100 band from $94,701</t>
+  </si>
+  <si>
+    <t>ar_phase_limit</t>
+  </si>
+  <si>
+    <t>97800</t>
+  </si>
+  <si>
+    <t>AR DFA 2025 Indexed Tax Brackets: last $100 band of the adjustment phase-in</t>
+  </si>
+  <si>
     <t>ar_standard_deduction_hoh</t>
   </si>
   <si>
-    <t>2410.0</t>
-  </si>
-  <si>
-    <t>AR standard deduction head of household (2025)</t>
+    <t>2470</t>
+  </si>
+  <si>
+    <t>AR standard deduction 2025, Head of Household (AR1000F instructions, line 27)</t>
   </si>
   <si>
     <t>ar_standard_deduction_joint</t>
   </si>
   <si>
-    <t>4820.0</t>
-  </si>
-  <si>
-    <t>AR standard deduction married filing jointly (2025)</t>
+    <t>4940</t>
+  </si>
+  <si>
+    <t>AR standard deduction 2025, Married Filing Joint (AR1000F instructions, line 27)</t>
   </si>
   <si>
     <t>ar_standard_deduction_mfs</t>
   </si>
   <si>
-    <t>AR standard deduction married filing separately (2025)</t>
+    <t>AR standard deduction 2025, Married Filing Separately (AR1000F instructions, line 27)</t>
   </si>
   <si>
     <t>ar_standard_deduction_single</t>
   </si>
   <si>
-    <t>AR standard deduction single (2025)</t>
+    <t>AR standard deduction 2025, Single (AR1000F instructions, line 27)</t>
+  </si>
+  <si>
+    <t>ar_state_tax</t>
+  </si>
+  <si>
+    <t>ar_std_deduction</t>
+  </si>
+  <si>
+    <t>ar_table_band_shift</t>
+  </si>
+  <si>
+    <t>75000</t>
+  </si>
+  <si>
+    <t>AR 2025 Regular Tax Table: below $75,000 its $100 bands run 00-99; the band ending at $75,000 is 74,900-75,000 inclusive and from there bands run 01-00 (75,001-75,100 ...)</t>
+  </si>
+  <si>
+    <t>ar_table_tax</t>
+  </si>
+  <si>
+    <t>ar_taxable_income</t>
+  </si>
+  <si>
+    <t>ar_top_adjust</t>
+  </si>
+  <si>
+    <t>89.30</t>
+  </si>
+  <si>
+    <t>AR DFA 2025 Indexed Tax Brackets: minus adjustment from $97,801 to $100,000</t>
   </si>
 </sst>
 </file>
@@ -863,184 +1143,152 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
+    <row r="9">
+      <c r="A9" s="5">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E11" s="1">
         <v>2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F11" s="1">
         <v>3</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G11" s="1">
         <v>4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H11" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I11" s="1">
         <v>6</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J11" s="1">
         <v>7</v>
       </c>
-      <c r="K10" s="1">
-        <v>8</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
         <v>9</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M11" s="1">
         <v>10</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N11" s="1">
         <v>11</v>
       </c>
-      <c r="O10" s="1">
+      <c r="O11" s="1">
         <v>12</v>
       </c>
-      <c r="P10" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="1">
+      <c r="Q11" s="1">
         <v>14</v>
       </c>
-      <c r="R10" s="1">
-        <v>15</v>
-      </c>
-      <c r="S10" s="1">
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5">
-        <v>1</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1049,61 +1297,61 @@
         <v>17</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -1159,58 +1407,58 @@
         <v>1</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -1218,58 +1466,58 @@
         <v>2</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -1277,62 +1525,298 @@
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>5</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:S1"/>
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A3:S3"/>
@@ -1341,7 +1825,8 @@
     <mergeCell ref="C6:S6"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:S8"/>
-    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A15:B15"/>
   </mergeCells>
 </worksheet>
@@ -1358,7 +1843,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1404,7 +1889,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1427,7 +1912,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1500,11 +1985,11 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -1557,11 +2042,11 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1632,6 +2117,1200 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5">
+        <v>1</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>7</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4">
+        <v>3</v>
+      </c>
+      <c r="G20" s="4">
+        <v>4</v>
+      </c>
+      <c r="H20" s="4">
+        <v>5</v>
+      </c>
+      <c r="I20" s="4">
+        <v>6</v>
+      </c>
+      <c r="J20" s="4">
+        <v>7</v>
+      </c>
+      <c r="K20" s="4">
+        <v>8</v>
+      </c>
+      <c r="L20" s="4">
+        <v>9</v>
+      </c>
+      <c r="M20" s="4">
+        <v>10</v>
+      </c>
+      <c r="N20" s="4">
+        <v>11</v>
+      </c>
+      <c r="O20" s="4">
+        <v>12</v>
+      </c>
+      <c r="P20" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>14</v>
+      </c>
+      <c r="R20" s="4">
+        <v>15</v>
+      </c>
+      <c r="S20" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>1</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>2</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5">
+        <v>3</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
+        <v>4</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5">
+        <v>5</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5">
+        <v>6</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5">
+        <v>7</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5">
+        <v>8</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:S8"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A20:B20"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="18"/>
     <col customWidth="true" max="2" min="2" width="25"/>
     <col customWidth="true" max="3" min="3" width="10"/>
@@ -1648,56 +3327,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1713,535 +3392,1355 @@
     </row>
     <row r="4">
       <c r="A4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>59</v>
+        <v>104</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>76</v>
+        <v>121</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>83</v>
+        <v>130</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M29" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
